--- a/SolarLights/SolarLights.xlsx
+++ b/SolarLights/SolarLights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomwatson/Documents/GitHub/Kicadprojects/SolarLights/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1C7A8A-69AE-9E4D-9D75-AEFF7195C65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDB29EA-4390-0C49-9FBB-373F6CF23CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="2340" windowWidth="27640" windowHeight="16680" xr2:uid="{A474EF1B-FD7D-D741-AB5A-955B159496C1}"/>
+    <workbookView xWindow="6560" yWindow="2340" windowWidth="27640" windowHeight="16680" xr2:uid="{A474EF1B-FD7D-D741-AB5A-955B159496C1}"/>
   </bookViews>
   <sheets>
     <sheet name="SolarLights" sheetId="1" r:id="rId1"/>
@@ -899,10 +899,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1758,23 +1757,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>4</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>40</v>
       </c>
     </row>
